--- a/01-projetos/01-data-project-foundations/data/input/absenteeism_data_38.xlsx
+++ b/01-projetos/01-data-project-foundations/data/input/absenteeism_data_38.xlsx
@@ -471,103 +471,103 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98968</v>
+        <v>95957</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sarah Caldeira</t>
+          <t>Julia Azevedo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Vendas</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Viagem de negócios</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45100</v>
+        <v>45101</v>
       </c>
       <c r="G2" t="n">
-        <v>10323.35</v>
+        <v>4299.11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97160</v>
+        <v>81669</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Marcelo Viana</t>
+          <t>Levi Azevedo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Recursos Humanos</t>
+          <t>Vendas</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45095</v>
+        <v>45088</v>
       </c>
       <c r="G3" t="n">
-        <v>11497.35</v>
+        <v>11231.76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>92406</v>
+        <v>63003</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Maria Eduarda Novaes</t>
+          <t>Ana Sophia Ramos</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Financeiro</t>
+          <t>Operações</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45085</v>
+        <v>45106</v>
       </c>
       <c r="G4" t="n">
-        <v>5530.39</v>
+        <v>4829.26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>47088</v>
+        <v>59390</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mariana Duarte</t>
+          <t>Arthur Nascimento</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jurídico</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -576,85 +576,85 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45085</v>
+        <v>45084</v>
       </c>
       <c r="G5" t="n">
-        <v>11550.95</v>
+        <v>11675.93</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>47553</v>
+        <v>7154</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bruna Azevedo</t>
+          <t>Nathan Rezende</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>P&amp;D</t>
+          <t>Vendas</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Viagem de negócios</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45085</v>
+        <v>45089</v>
       </c>
       <c r="G6" t="n">
-        <v>12458.92</v>
+        <v>6523.44</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>64689</v>
+        <v>25323</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sra. Larissa Farias</t>
+          <t>Carolina Carvalho</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Atendimento ao Cliente</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45098</v>
+        <v>45092</v>
       </c>
       <c r="G7" t="n">
-        <v>4229.83</v>
+        <v>12258.52</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>35807</v>
+        <v>88935</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Enzo Gabriel Rodrigues</t>
+          <t>Breno Peixoto</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>Recursos Humanos</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -663,85 +663,85 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45097</v>
+        <v>45105</v>
       </c>
       <c r="G8" t="n">
-        <v>8658.17</v>
+        <v>4161.98</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>57576</v>
+        <v>69987</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Elisa Melo</t>
+          <t>Lorenzo Rocha</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Financeiro</t>
+          <t>Recursos Humanos</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Viagem de negócios</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>7</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45089</v>
+        <v>45101</v>
       </c>
       <c r="G9" t="n">
-        <v>11031.22</v>
+        <v>7125.76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>69572</v>
+        <v>61588</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Srta. Sophie Fernandes</t>
+          <t>Marcos Vinicius Santos</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Recursos Humanos</t>
+          <t>P&amp;D</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Consulta médica</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45080</v>
+        <v>45091</v>
       </c>
       <c r="G10" t="n">
-        <v>9132.059999999999</v>
+        <v>9208.32</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>42478</v>
+        <v>55332</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Maria Sophia Mendes</t>
+          <t>Dr. Anthony da Luz</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atendimento ao Cliente</t>
+          <t>Jurídico</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45087</v>
+        <v>45089</v>
       </c>
       <c r="G11" t="n">
-        <v>6101.89</v>
+        <v>10283.39</v>
       </c>
     </row>
   </sheetData>
